--- a/test-cases-reports/baseline Load testing/baseline_load_test_report.xlsx
+++ b/test-cases-reports/baseline Load testing/baseline_load_test_report.xlsx
@@ -409,7 +409,7 @@
     <t>Report Date</t>
   </si>
   <si>
-    <t>18/6/2026, 8:18:39 pm</t>
+    <t>19/6/2026, 5:21:49 am</t>
   </si>
   <si>
     <t>📦 Install k6</t>

--- a/test-cases-reports/baseline Load testing/baseline_load_test_report.xlsx
+++ b/test-cases-reports/baseline Load testing/baseline_load_test_report.xlsx
@@ -409,7 +409,7 @@
     <t>Report Date</t>
   </si>
   <si>
-    <t>19/6/2026, 5:21:49 am</t>
+    <t>20/7/2026, 11:01:17 pm</t>
   </si>
   <si>
     <t>📦 Install k6</t>
